--- a/media/exports/reports/2026-10/growth-services.xlsx
+++ b/media/exports/reports/2026-10/growth-services.xlsx
@@ -818,7 +818,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
     <row r="9" ht="75" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>October is still in progress and wages are paid fortnightly, so a part month can't be bridged: this is September, the latest closed month. September's client work made $68,410 gross margin (51.9%). Consultant time not charged to client work took $660 and overheads $52,140, leaving $15,610 profit before tax (11.8% of revenue). To cover overheads, client work needs a 40.0% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
+          <t>October is still in progress and wages are paid fortnightly, so a part month can't be bridged: this is September, the latest closed month. September's client work made $81,890 gross margin (56.3%). Consultant time not charged to client work took $14,352 and overheads $52,140, leaving $15,398 profit before tax (10.6% of revenue). To cover overheads, client work needs a 45.8% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
         </is>
       </c>
     </row>
@@ -860,10 +860,10 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="75" customHeight="1">
+    <row r="12" ht="90" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Gross margin is not profit. Gross margin = revenue less contractors and consultant time charged to the work at $60 an hour (wages and all on-costs). Not included: consultant time not charged to clients, and overheads (management and admin wages, marketing, rent, IT, insurance, travel, depreciation, interest). Profit is what's left after those. Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>Gross margin is not profit. Gross margin = revenue less contractors and consultant time charged to the work at $60 an hour (wages and all on-costs). Not included: consultant time not charged to clients, and overheads (management and admin wages, marketing, rent, IT, insurance, travel, depreciation, interest). Profit is what's left after those. Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>$44,605 against $71,260</t>
+          <t>$49,055 against $78,550</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>$411,850 against $278,590</t>
+          <t>$454,340 against $306,750</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>$248,170 before overheads</t>
+          <t>$290,660 before overheads</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
     <row r="21" ht="45" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Revenue is 47.8% up on the same period last year, year to date ($411,850 against $278,590). Retainers make the highest gross margin (68.5%); Projects the lowest (56.3%). The business needs 40.0% gross margin just to cover overheads.</t>
+          <t>Revenue is 48.1% up on the same period last year, year to date ($454,340 against $306,750). Retainers make the highest gross margin (71.3%); Projects the lowest (60.5%). The business needs 45.8% gross margin just to cover overheads.</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
     <row r="24" ht="45" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Projects: 56.3% gross margin, 16.3 points over the 40.0% target ($41,250 ahead on $253,250 this financial year to date). Retainers: 68.5% gross margin, 28.5 points over the 40.0% target ($37,020 ahead on $130,000 this financial year to date).</t>
+          <t>Projects: 60.5% gross margin, 20.5 points over the 40.0% target ($57,324 ahead on $280,040 this financial year to date). Retainers: 71.3% gross margin, 31.3 points over the 40.0% target ($44,700 ahead on $142,800 this financial year to date).</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>$12,105 against $45,860</t>
+          <t>$13,355 against $50,650</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>$253,250 against $187,490</t>
+          <t>$280,040 against $206,750</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>$142,550 before overheads</t>
+          <t>$169,340 before overheads</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Projects brought in $253,250 this financial year to date, 35.1% on the same period last year (slower than the business as a whole, 47.8%), at a 56.3% gross margin (below the 60.3% overall).</t>
+          <t>Projects brought in $280,040 this financial year to date, 35.4% on the same period last year (slower than the business as a whole, 48.1%), at a 60.5% gross margin (below the 64.0% overall).</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Projects: 56.3% gross margin, 16.3 points over the 40.0% target ($41,250 ahead on $253,250 this financial year to date).</t>
+          <t>Projects: 60.5% gross margin, 20.5 points over the 40.0% target ($57,324 ahead on $280,040 this financial year to date).</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>$32,500 against $16,300</t>
+          <t>$35,700 against $17,900</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>$130,000 against $65,200</t>
+          <t>$142,800 against $71,600</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>$89,020 before overheads</t>
+          <t>$101,820 before overheads</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
     <row r="45" ht="45" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Retainers brought in $130,000 this financial year to date, 99.4% on the same period last year (faster than the business as a whole, 47.8%), at a 68.5% gross margin (above the 60.3% overall).</t>
+          <t>Retainers brought in $142,800 this financial year to date, 99.4% on the same period last year (faster than the business as a whole, 48.1%), at a 71.3% gross margin (above the 64.0% overall).</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Retainers: 68.5% gross margin, 28.5 points over the 40.0% target ($37,020 ahead on $130,000 this financial year to date).</t>
+          <t>Retainers: 71.3% gross margin, 31.3 points over the 40.0% target ($44,700 ahead on $142,800 this financial year to date).</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>$0 against $9,100</t>
+          <t>$0 against $10,000</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>$28,600 against $25,900</t>
+          <t>$31,500 against $28,400</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>$16,600 before overheads</t>
+          <t>$19,500 before overheads</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>Training brought in $28,600 this financial year to date, 10.4% on the same period last year (slower than the business as a whole, 47.8%), at a 58.0% gross margin (below the 60.3% overall).</t>
+          <t>Training brought in $31,500 this financial year to date, 10.9% on the same period last year (slower than the business as a whole, 48.1%), at a 61.9% gross margin (below the 64.0% overall).</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>Training: 58.0% gross margin, 18.0 points over the 40.0% target ($5,160 ahead on $28,600 this financial year to date).</t>
+          <t>Training: 61.9% gross margin, 21.9 points over the 40.0% target ($6,900 ahead on $31,500 this financial year to date).</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1360,7 +1360,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>68410</v>
+        <v>81890</v>
       </c>
     </row>
     <row r="9">
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>46500</v>
+        <v>60192</v>
       </c>
     </row>
     <row r="10">
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>131850</v>
+        <v>145330</v>
       </c>
     </row>
     <row r="16">
@@ -1506,7 +1506,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Ties to the September 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave. October is still in progress, so this uses September.</t>
+          <t>Ties to the September 2026 P&amp;L (locked). Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold. October is still in progress, so this uses September.</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="B25" s="12" t="n">
-        <v>44605</v>
+        <v>49055</v>
       </c>
     </row>
     <row r="26">
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>71260</v>
+        <v>78550</v>
       </c>
     </row>
     <row r="27">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="B34" s="12" t="n">
-        <v>411850</v>
+        <v>454340</v>
       </c>
     </row>
     <row r="35">
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="B35" s="12" t="n">
-        <v>278590</v>
+        <v>306750</v>
       </c>
     </row>
     <row r="36">
@@ -1634,7 +1634,7 @@
         </is>
       </c>
       <c r="B37" s="12" t="n">
-        <v>248170</v>
+        <v>290660</v>
       </c>
     </row>
     <row r="38">
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="B45" s="12" t="n">
-        <v>411850</v>
+        <v>454340</v>
       </c>
     </row>
     <row r="46">
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="B46" s="12" t="n">
-        <v>278590</v>
+        <v>306750</v>
       </c>
     </row>
     <row r="47">
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="B48" s="12" t="n">
-        <v>248170</v>
+        <v>290660</v>
       </c>
     </row>
     <row r="49">
@@ -1769,7 +1769,7 @@
         </is>
       </c>
       <c r="B56" s="12" t="n">
-        <v>12105</v>
+        <v>13355</v>
       </c>
     </row>
     <row r="57">
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="B57" s="12" t="n">
-        <v>45860</v>
+        <v>50650</v>
       </c>
     </row>
     <row r="58">
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B65" s="12" t="n">
-        <v>253250</v>
+        <v>280040</v>
       </c>
     </row>
     <row r="66">
@@ -1841,7 +1841,7 @@
         </is>
       </c>
       <c r="B66" s="12" t="n">
-        <v>187490</v>
+        <v>206750</v>
       </c>
     </row>
     <row r="67">
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="B68" s="12" t="n">
-        <v>142550</v>
+        <v>169340</v>
       </c>
     </row>
     <row r="69">
@@ -1914,7 +1914,7 @@
         </is>
       </c>
       <c r="B76" s="12" t="n">
-        <v>253250</v>
+        <v>280040</v>
       </c>
     </row>
     <row r="77">
@@ -1924,7 +1924,7 @@
         </is>
       </c>
       <c r="B77" s="12" t="n">
-        <v>187490</v>
+        <v>206750</v>
       </c>
     </row>
     <row r="78">
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="B79" s="12" t="n">
-        <v>142550</v>
+        <v>169340</v>
       </c>
     </row>
     <row r="80">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="B87" s="12" t="n">
-        <v>32500</v>
+        <v>35700</v>
       </c>
     </row>
     <row r="88">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="B88" s="12" t="n">
-        <v>16300</v>
+        <v>17900</v>
       </c>
     </row>
     <row r="89">
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="B96" s="12" t="n">
-        <v>130000</v>
+        <v>142800</v>
       </c>
     </row>
     <row r="97">
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="B97" s="12" t="n">
-        <v>65200</v>
+        <v>71600</v>
       </c>
     </row>
     <row r="98">
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="B99" s="12" t="n">
-        <v>89020</v>
+        <v>101820</v>
       </c>
     </row>
     <row r="100">
@@ -2142,7 +2142,7 @@
         </is>
       </c>
       <c r="B107" s="12" t="n">
-        <v>130000</v>
+        <v>142800</v>
       </c>
     </row>
     <row r="108">
@@ -2152,7 +2152,7 @@
         </is>
       </c>
       <c r="B108" s="12" t="n">
-        <v>65200</v>
+        <v>71600</v>
       </c>
     </row>
     <row r="109">
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="B110" s="12" t="n">
-        <v>89020</v>
+        <v>101820</v>
       </c>
     </row>
     <row r="111">
@@ -2235,7 +2235,7 @@
         </is>
       </c>
       <c r="B119" s="12" t="n">
-        <v>9100</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="120">
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="B127" s="12" t="n">
-        <v>28600</v>
+        <v>31500</v>
       </c>
     </row>
     <row r="128">
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="B128" s="12" t="n">
-        <v>25900</v>
+        <v>28400</v>
       </c>
     </row>
     <row r="129">
@@ -2318,7 +2318,7 @@
         </is>
       </c>
       <c r="B130" s="12" t="n">
-        <v>16600</v>
+        <v>19500</v>
       </c>
     </row>
     <row r="131">
@@ -2370,7 +2370,7 @@
         </is>
       </c>
       <c r="B138" s="12" t="n">
-        <v>28600</v>
+        <v>31500</v>
       </c>
     </row>
     <row r="139">
@@ -2380,7 +2380,7 @@
         </is>
       </c>
       <c r="B139" s="12" t="n">
-        <v>25900</v>
+        <v>28400</v>
       </c>
     </row>
     <row r="140">
@@ -2401,7 +2401,7 @@
         </is>
       </c>
       <c r="B141" s="12" t="n">
-        <v>16600</v>
+        <v>19500</v>
       </c>
     </row>
     <row r="142">
@@ -2431,7 +2431,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2481,7 +2481,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -2540,7 +2540,7 @@
         </is>
       </c>
       <c r="D6" s="12" t="n">
-        <v>108140</v>
+        <v>118390</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>40040</v>
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="D7" s="12" t="n">
-        <v>114895</v>
+        <v>125715</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>42940</v>
@@ -2602,7 +2602,7 @@
         </is>
       </c>
       <c r="D8" s="12" t="n">
-        <v>88250</v>
+        <v>96560</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>33260</v>
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="D9" s="12" t="n">
-        <v>111010</v>
+        <v>121275</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>42820</v>
@@ -2664,7 +2664,7 @@
         </is>
       </c>
       <c r="D10" s="12" t="n">
-        <v>77175</v>
+        <v>84340</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>31940</v>
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="D11" s="12" t="n">
-        <v>63970</v>
+        <v>69985</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>25520</v>
@@ -2726,7 +2726,7 @@
         </is>
       </c>
       <c r="D12" s="12" t="n">
-        <v>95555</v>
+        <v>104970</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>36100</v>
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="D13" s="12" t="n">
-        <v>90220</v>
+        <v>99060</v>
       </c>
       <c r="E13" s="12" t="n">
         <v>35380</v>
@@ -2788,7 +2788,7 @@
         </is>
       </c>
       <c r="D14" s="12" t="n">
-        <v>86320</v>
+        <v>94805</v>
       </c>
       <c r="E14" s="12" t="n">
         <v>32820</v>
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="D15" s="12" t="n">
-        <v>61475</v>
+        <v>67745</v>
       </c>
       <c r="E15" s="12" t="n">
         <v>21360</v>
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="D16" s="12" t="n">
-        <v>59535</v>
+        <v>65650</v>
       </c>
       <c r="E16" s="12" t="n">
         <v>20280</v>
@@ -2881,7 +2881,7 @@
         </is>
       </c>
       <c r="D17" s="12" t="n">
-        <v>71260</v>
+        <v>78550</v>
       </c>
       <c r="E17" s="12" t="n">
         <v>25540</v>
@@ -2912,7 +2912,7 @@
         </is>
       </c>
       <c r="D18" s="12" t="n">
-        <v>83940</v>
+        <v>92575</v>
       </c>
       <c r="E18" s="12" t="n">
         <v>31140</v>
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="D19" s="12" t="n">
-        <v>69420</v>
+        <v>76600</v>
       </c>
       <c r="E19" s="12" t="n">
         <v>24520</v>
@@ -2974,7 +2974,7 @@
         </is>
       </c>
       <c r="D20" s="12" t="n">
-        <v>92370</v>
+        <v>102350</v>
       </c>
       <c r="E20" s="12" t="n">
         <v>32520</v>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="D21" s="12" t="n">
-        <v>100055</v>
+        <v>110835</v>
       </c>
       <c r="E21" s="12" t="n">
         <v>36580</v>
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="D22" s="12" t="n">
-        <v>109865</v>
+        <v>121215</v>
       </c>
       <c r="E22" s="12" t="n">
         <v>40720</v>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="D23" s="12" t="n">
-        <v>80590</v>
+        <v>88665</v>
       </c>
       <c r="E23" s="12" t="n">
         <v>27860</v>
@@ -3098,7 +3098,7 @@
         </is>
       </c>
       <c r="D24" s="12" t="n">
-        <v>77090</v>
+        <v>84920</v>
       </c>
       <c r="E24" s="12" t="n">
         <v>27680</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="D25" s="12" t="n">
-        <v>115550</v>
+        <v>127580</v>
       </c>
       <c r="E25" s="12" t="n">
         <v>46060</v>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="D26" s="12" t="n">
-        <v>120755</v>
+        <v>133455</v>
       </c>
       <c r="E26" s="12" t="n">
         <v>47680</v>
@@ -3191,7 +3191,7 @@
         </is>
       </c>
       <c r="D27" s="12" t="n">
-        <v>114640</v>
+        <v>126500</v>
       </c>
       <c r="E27" s="12" t="n">
         <v>46620</v>
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="D28" s="12" t="n">
-        <v>131850</v>
+        <v>145330</v>
       </c>
       <c r="E28" s="12" t="n">
         <v>63440</v>
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="D29" s="12" t="n">
-        <v>44605</v>
+        <v>49055</v>
       </c>
       <c r="E29" s="12" t="n">
         <v>5940</v>
@@ -3284,7 +3284,7 @@
         </is>
       </c>
       <c r="D30" s="12" t="n">
-        <v>88540</v>
+        <v>96790</v>
       </c>
       <c r="E30" s="12" t="n">
         <v>34400</v>
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="D31" s="12" t="n">
-        <v>94695</v>
+        <v>103515</v>
       </c>
       <c r="E31" s="12" t="n">
         <v>36880</v>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="D32" s="12" t="n">
-        <v>66850</v>
+        <v>73060</v>
       </c>
       <c r="E32" s="12" t="n">
         <v>26240</v>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="D33" s="12" t="n">
-        <v>84410</v>
+        <v>92075</v>
       </c>
       <c r="E33" s="12" t="n">
         <v>34360</v>
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="D34" s="12" t="n">
-        <v>48975</v>
+        <v>53340</v>
       </c>
       <c r="E34" s="12" t="n">
         <v>21860</v>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="D35" s="12" t="n">
-        <v>37570</v>
+        <v>40885</v>
       </c>
       <c r="E35" s="12" t="n">
         <v>17660</v>
@@ -3470,7 +3470,7 @@
         </is>
       </c>
       <c r="D36" s="12" t="n">
-        <v>59755</v>
+        <v>65570</v>
       </c>
       <c r="E36" s="12" t="n">
         <v>23980</v>
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="D37" s="12" t="n">
-        <v>64520</v>
+        <v>70760</v>
       </c>
       <c r="E37" s="12" t="n">
         <v>26860</v>
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="D38" s="12" t="n">
-        <v>64820</v>
+        <v>71205</v>
       </c>
       <c r="E38" s="12" t="n">
         <v>25920</v>
@@ -3563,7 +3563,7 @@
         </is>
       </c>
       <c r="D39" s="12" t="n">
-        <v>38775</v>
+        <v>42845</v>
       </c>
       <c r="E39" s="12" t="n">
         <v>13860</v>
@@ -3594,7 +3594,7 @@
         </is>
       </c>
       <c r="D40" s="12" t="n">
-        <v>38035</v>
+        <v>42050</v>
       </c>
       <c r="E40" s="12" t="n">
         <v>13560</v>
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="D41" s="12" t="n">
-        <v>45860</v>
+        <v>50650</v>
       </c>
       <c r="E41" s="12" t="n">
         <v>18220</v>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="D42" s="12" t="n">
-        <v>46840</v>
+        <v>51775</v>
       </c>
       <c r="E42" s="12" t="n">
         <v>18960</v>
@@ -3687,7 +3687,7 @@
         </is>
       </c>
       <c r="D43" s="12" t="n">
-        <v>29520</v>
+        <v>32800</v>
       </c>
       <c r="E43" s="12" t="n">
         <v>12340</v>
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="D44" s="12" t="n">
-        <v>60170</v>
+        <v>66950</v>
       </c>
       <c r="E44" s="12" t="n">
         <v>22440</v>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="D45" s="12" t="n">
-        <v>62955</v>
+        <v>70035</v>
       </c>
       <c r="E45" s="12" t="n">
         <v>23440</v>
@@ -3780,7 +3780,7 @@
         </is>
       </c>
       <c r="D46" s="12" t="n">
-        <v>75165</v>
+        <v>83115</v>
       </c>
       <c r="E46" s="12" t="n">
         <v>29380</v>
@@ -3811,7 +3811,7 @@
         </is>
       </c>
       <c r="D47" s="12" t="n">
-        <v>47090</v>
+        <v>51865</v>
       </c>
       <c r="E47" s="12" t="n">
         <v>17480</v>
@@ -3842,7 +3842,7 @@
         </is>
       </c>
       <c r="D48" s="12" t="n">
-        <v>43590</v>
+        <v>48120</v>
       </c>
       <c r="E48" s="12" t="n">
         <v>16220</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="D49" s="12" t="n">
-        <v>76650</v>
+        <v>84880</v>
       </c>
       <c r="E49" s="12" t="n">
         <v>31780</v>
@@ -3904,7 +3904,7 @@
         </is>
       </c>
       <c r="D50" s="12" t="n">
-        <v>79455</v>
+        <v>88055</v>
       </c>
       <c r="E50" s="12" t="n">
         <v>32080</v>
@@ -3935,7 +3935,7 @@
         </is>
       </c>
       <c r="D51" s="12" t="n">
-        <v>75740</v>
+        <v>83800</v>
       </c>
       <c r="E51" s="12" t="n">
         <v>31680</v>
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="D52" s="12" t="n">
-        <v>85950</v>
+        <v>94830</v>
       </c>
       <c r="E52" s="12" t="n">
         <v>42800</v>
@@ -3997,7 +3997,7 @@
         </is>
       </c>
       <c r="D53" s="12" t="n">
-        <v>12105</v>
+        <v>13355</v>
       </c>
       <c r="E53" s="12" t="n">
         <v>4140</v>
@@ -4028,7 +4028,7 @@
         </is>
       </c>
       <c r="D54" s="12" t="n">
-        <v>15000</v>
+        <v>16500</v>
       </c>
       <c r="E54" s="12" t="n">
         <v>4800</v>
@@ -4059,7 +4059,7 @@
         </is>
       </c>
       <c r="D55" s="12" t="n">
-        <v>15000</v>
+        <v>16500</v>
       </c>
       <c r="E55" s="12" t="n">
         <v>5100</v>
@@ -4090,7 +4090,7 @@
         </is>
       </c>
       <c r="D56" s="12" t="n">
-        <v>15000</v>
+        <v>16500</v>
       </c>
       <c r="E56" s="12" t="n">
         <v>4920</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="D57" s="12" t="n">
-        <v>15000</v>
+        <v>16500</v>
       </c>
       <c r="E57" s="12" t="n">
         <v>5400</v>
@@ -4152,7 +4152,7 @@
         </is>
       </c>
       <c r="D58" s="12" t="n">
-        <v>21800</v>
+        <v>24000</v>
       </c>
       <c r="E58" s="12" t="n">
         <v>7980</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="D59" s="12" t="n">
-        <v>21800</v>
+        <v>24000</v>
       </c>
       <c r="E59" s="12" t="n">
         <v>7020</v>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="D60" s="12" t="n">
-        <v>21800</v>
+        <v>24000</v>
       </c>
       <c r="E60" s="12" t="n">
         <v>8460</v>
@@ -4245,7 +4245,7 @@
         </is>
       </c>
       <c r="D61" s="12" t="n">
-        <v>21800</v>
+        <v>24000</v>
       </c>
       <c r="E61" s="12" t="n">
         <v>7800</v>
@@ -4276,7 +4276,7 @@
         </is>
       </c>
       <c r="D62" s="12" t="n">
-        <v>16300</v>
+        <v>17900</v>
       </c>
       <c r="E62" s="12" t="n">
         <v>5940</v>
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="D63" s="12" t="n">
-        <v>16300</v>
+        <v>17900</v>
       </c>
       <c r="E63" s="12" t="n">
         <v>5400</v>
@@ -4338,7 +4338,7 @@
         </is>
       </c>
       <c r="D64" s="12" t="n">
-        <v>16300</v>
+        <v>17900</v>
       </c>
       <c r="E64" s="12" t="n">
         <v>5760</v>
@@ -4369,7 +4369,7 @@
         </is>
       </c>
       <c r="D65" s="12" t="n">
-        <v>16300</v>
+        <v>17900</v>
       </c>
       <c r="E65" s="12" t="n">
         <v>5640</v>
@@ -4400,7 +4400,7 @@
         </is>
       </c>
       <c r="D66" s="12" t="n">
-        <v>28300</v>
+        <v>31100</v>
       </c>
       <c r="E66" s="12" t="n">
         <v>9480</v>
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="D67" s="12" t="n">
-        <v>28300</v>
+        <v>31100</v>
       </c>
       <c r="E67" s="12" t="n">
         <v>9120</v>
@@ -4462,7 +4462,7 @@
         </is>
       </c>
       <c r="D68" s="12" t="n">
-        <v>28300</v>
+        <v>31100</v>
       </c>
       <c r="E68" s="12" t="n">
         <v>9360</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="D69" s="12" t="n">
-        <v>28300</v>
+        <v>31100</v>
       </c>
       <c r="E69" s="12" t="n">
         <v>10440</v>
@@ -4524,7 +4524,7 @@
         </is>
       </c>
       <c r="D70" s="12" t="n">
-        <v>28300</v>
+        <v>31100</v>
       </c>
       <c r="E70" s="12" t="n">
         <v>9240</v>
@@ -4555,7 +4555,7 @@
         </is>
       </c>
       <c r="D71" s="12" t="n">
-        <v>28300</v>
+        <v>31100</v>
       </c>
       <c r="E71" s="12" t="n">
         <v>9420</v>
@@ -4586,7 +4586,7 @@
         </is>
       </c>
       <c r="D72" s="12" t="n">
-        <v>28300</v>
+        <v>31100</v>
       </c>
       <c r="E72" s="12" t="n">
         <v>10500</v>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="D73" s="12" t="n">
-        <v>32500</v>
+        <v>35700</v>
       </c>
       <c r="E73" s="12" t="n">
         <v>12180</v>
@@ -4648,7 +4648,7 @@
         </is>
       </c>
       <c r="D74" s="12" t="n">
-        <v>32500</v>
+        <v>35700</v>
       </c>
       <c r="E74" s="12" t="n">
         <v>12900</v>
@@ -4679,7 +4679,7 @@
         </is>
       </c>
       <c r="D75" s="12" t="n">
-        <v>32500</v>
+        <v>35700</v>
       </c>
       <c r="E75" s="12" t="n">
         <v>12840</v>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="D76" s="12" t="n">
-        <v>32500</v>
+        <v>35700</v>
       </c>
       <c r="E76" s="12" t="n">
         <v>13440</v>
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="D77" s="12" t="n">
-        <v>32500</v>
+        <v>35700</v>
       </c>
       <c r="E77" s="12" t="n">
         <v>1800</v>
@@ -4772,7 +4772,7 @@
         </is>
       </c>
       <c r="D78" s="12" t="n">
-        <v>4600</v>
+        <v>5100</v>
       </c>
       <c r="E78" s="12" t="n">
         <v>840</v>
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="D79" s="12" t="n">
-        <v>5200</v>
+        <v>5700</v>
       </c>
       <c r="E79" s="12" t="n">
         <v>960</v>
@@ -4834,7 +4834,7 @@
         </is>
       </c>
       <c r="D80" s="12" t="n">
-        <v>6400</v>
+        <v>7000</v>
       </c>
       <c r="E80" s="12" t="n">
         <v>2100</v>
@@ -4865,7 +4865,7 @@
         </is>
       </c>
       <c r="D81" s="12" t="n">
-        <v>11600</v>
+        <v>12700</v>
       </c>
       <c r="E81" s="12" t="n">
         <v>3060</v>
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="D82" s="12" t="n">
-        <v>6400</v>
+        <v>7000</v>
       </c>
       <c r="E82" s="12" t="n">
         <v>2100</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="D83" s="12" t="n">
-        <v>4600</v>
+        <v>5100</v>
       </c>
       <c r="E83" s="12" t="n">
         <v>840</v>
@@ -4958,7 +4958,7 @@
         </is>
       </c>
       <c r="D84" s="12" t="n">
-        <v>14000</v>
+        <v>15400</v>
       </c>
       <c r="E84" s="12" t="n">
         <v>3660</v>
@@ -4989,7 +4989,7 @@
         </is>
       </c>
       <c r="D85" s="12" t="n">
-        <v>3900</v>
+        <v>4300</v>
       </c>
       <c r="E85" s="12" t="n">
         <v>720</v>
@@ -5020,7 +5020,7 @@
         </is>
       </c>
       <c r="D86" s="12" t="n">
-        <v>5200</v>
+        <v>5700</v>
       </c>
       <c r="E86" s="12" t="n">
         <v>960</v>
@@ -5051,7 +5051,7 @@
         </is>
       </c>
       <c r="D87" s="12" t="n">
-        <v>6400</v>
+        <v>7000</v>
       </c>
       <c r="E87" s="12" t="n">
         <v>2100</v>
@@ -5082,7 +5082,7 @@
         </is>
       </c>
       <c r="D88" s="12" t="n">
-        <v>5200</v>
+        <v>5700</v>
       </c>
       <c r="E88" s="12" t="n">
         <v>960</v>
@@ -5113,7 +5113,7 @@
         </is>
       </c>
       <c r="D89" s="12" t="n">
-        <v>9100</v>
+        <v>10000</v>
       </c>
       <c r="E89" s="12" t="n">
         <v>1680</v>
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="D90" s="12" t="n">
-        <v>8800</v>
+        <v>9700</v>
       </c>
       <c r="E90" s="12" t="n">
         <v>2700</v>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="D91" s="12" t="n">
-        <v>11600</v>
+        <v>12700</v>
       </c>
       <c r="E91" s="12" t="n">
         <v>3060</v>
@@ -5206,7 +5206,7 @@
         </is>
       </c>
       <c r="D92" s="12" t="n">
-        <v>3900</v>
+        <v>4300</v>
       </c>
       <c r="E92" s="12" t="n">
         <v>720</v>
@@ -5237,7 +5237,7 @@
         </is>
       </c>
       <c r="D93" s="12" t="n">
-        <v>8800</v>
+        <v>9700</v>
       </c>
       <c r="E93" s="12" t="n">
         <v>2700</v>
@@ -5268,7 +5268,7 @@
         </is>
       </c>
       <c r="D94" s="12" t="n">
-        <v>6400</v>
+        <v>7000</v>
       </c>
       <c r="E94" s="12" t="n">
         <v>2100</v>
@@ -5299,7 +5299,7 @@
         </is>
       </c>
       <c r="D95" s="12" t="n">
-        <v>5200</v>
+        <v>5700</v>
       </c>
       <c r="E95" s="12" t="n">
         <v>960</v>
@@ -5330,7 +5330,7 @@
         </is>
       </c>
       <c r="D96" s="12" t="n">
-        <v>5200</v>
+        <v>5700</v>
       </c>
       <c r="E96" s="12" t="n">
         <v>960</v>
@@ -5361,7 +5361,7 @@
         </is>
       </c>
       <c r="D97" s="12" t="n">
-        <v>6400</v>
+        <v>7000</v>
       </c>
       <c r="E97" s="12" t="n">
         <v>2100</v>
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="D98" s="12" t="n">
-        <v>8800</v>
+        <v>9700</v>
       </c>
       <c r="E98" s="12" t="n">
         <v>2700</v>
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="D99" s="12" t="n">
-        <v>6400</v>
+        <v>7000</v>
       </c>
       <c r="E99" s="12" t="n">
         <v>2100</v>
@@ -5454,7 +5454,7 @@
         </is>
       </c>
       <c r="D100" s="12" t="n">
-        <v>13400</v>
+        <v>14800</v>
       </c>
       <c r="E100" s="12" t="n">
         <v>7200</v>
@@ -5505,7 +5505,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -5557,7 +5557,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -5601,17 +5601,17 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>253250</v>
+        <v>280040</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>187490</v>
+        <v>206750</v>
       </c>
       <c r="D6" s="13">
         <f>IF(C6=0,"",B6/C6-1)</f>
         <v/>
       </c>
       <c r="E6" s="12" t="n">
-        <v>142550</v>
+        <v>169340</v>
       </c>
       <c r="F6" s="13">
         <f>IF(B6=0,"",E6/B6)</f>
@@ -5625,17 +5625,17 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>130000</v>
+        <v>142800</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>65200</v>
+        <v>71600</v>
       </c>
       <c r="D7" s="13">
         <f>IF(C7=0,"",B7/C7-1)</f>
         <v/>
       </c>
       <c r="E7" s="12" t="n">
-        <v>89020</v>
+        <v>101820</v>
       </c>
       <c r="F7" s="13">
         <f>IF(B7=0,"",E7/B7)</f>
@@ -5649,17 +5649,17 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>28600</v>
+        <v>31500</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>25900</v>
+        <v>28400</v>
       </c>
       <c r="D8" s="13">
         <f>IF(C8=0,"",B8/C8-1)</f>
         <v/>
       </c>
       <c r="E8" s="12" t="n">
-        <v>16600</v>
+        <v>19500</v>
       </c>
       <c r="F8" s="13">
         <f>IF(B8=0,"",E8/B8)</f>
@@ -5673,17 +5673,17 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>411850</v>
+        <v>454340</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>278590</v>
+        <v>306750</v>
       </c>
       <c r="D9" s="13">
         <f>IF(C9=0,"",B9/C9-1)</f>
         <v/>
       </c>
       <c r="E9" s="12" t="n">
-        <v>248170</v>
+        <v>290660</v>
       </c>
       <c r="F9" s="13">
         <f>IF(B9=0,"",E9/B9)</f>
@@ -5696,7 +5696,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2026-10/growth-services.xlsx
+++ b/media/exports/reports/2026-10/growth-services.xlsx
@@ -818,7 +818,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B17" s="9">
-        <f>Workings!B38</f>
+        <f>Workings!B36</f>
         <v/>
       </c>
       <c r="C17" s="10" t="inlineStr">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B29" s="9">
-        <f>Workings!B69</f>
+        <f>Workings!B67</f>
         <v/>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="B41" s="9">
-        <f>Workings!B100</f>
+        <f>Workings!B98</f>
         <v/>
       </c>
       <c r="C41" s="10" t="inlineStr">
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="B53" s="9">
-        <f>Workings!B131</f>
+        <f>Workings!B129</f>
         <v/>
       </c>
       <c r="C53" s="10" t="inlineStr">
@@ -1315,7 +1315,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1360,7 +1360,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2481,7 +2481,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -5505,7 +5505,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -5557,7 +5557,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: October 2026 to date · Data status: Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Advisory Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-services.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
